--- a/output/上海板块学区融合总表.xlsx
+++ b/output/上海板块学区融合总表.xlsx
@@ -8,15 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="融合总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="入选看房清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="十六区策略总览" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="评分图例与融合规则" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="双源校准说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="升学政策总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="幼升小政策" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="小升初政策" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="中考政策" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="入选看房清单" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="十六区策略总览" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="评分图例与融合规则" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="双源校准说明" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'融合总表'!$A$5:$V$111</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'融合总表'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'入选看房清单'!$A$4:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'入选看房清单'!$A$4:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +124,35 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -184,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -206,11 +239,44 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -293,6 +359,35 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -705,37 +800,37 @@
           <t>板块样本  106</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="32" t="n"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>强烈推荐  15</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="32" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>可考虑  23</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="32" t="n"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>谨慎  21</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
+      <c r="H3" s="32" t="n"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>排除  47</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
+      <c r="J3" s="32" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>本轮入选看房  18</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n"/>
+      <c r="L3" s="32" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -11381,6 +11476,2189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>上海升学政策总览（幼升小 · 小升初 · 中考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本册政策页服务于学区选房决策。权威原文以市教委、各区教育局、上海教育考试院当年文件为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>一、三阶段对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>入学/录取逻辑</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>关键机制</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>买房最相关变量</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>纪要策略位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>幼升小</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>免试就近；人户一致优先</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>公民办二选一；民办摇号</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>人户一致+入户年限+五年一户</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>现在必须解决（明年入学）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>小升初</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>对口 / 派位 / 回户籍</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>公民办同步；民办摇号</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>学籍对口区几乎绑定小学</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>可分步：小学后再置换</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>中考</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>全市统考+分批次录取</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>自招→名额分配→统一招生</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>报名区竞争与名额结构</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>不必用学区房锁定高中</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>二、购房决策检查清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>操作要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>幼升小买房</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>优先保证「人户一致」且满足目标校入户/房产年限；明年入学则倒推能否赶上登记截止日与验证要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>五年一户</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>同一套房子可能五年内只能送一孩进同一所对口小学；二孩家庭或准备出售/挂靠者务必查清</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>小升初</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>学籍对口区：小学选择几乎决定初中；户籍对口区：更可考虑小学后再搬家换初中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>九年一贯</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>复旦附属等常见要求户籍房产一致且提前约3年；时间不够不要硬冲</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>中考</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>不靠学区房锁定高中；关注报名所在区的名额分配结构与竞争生态</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>随迁/积分</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>非沪籍路径与沪籍完全不同；积分、居住证、社保断缴风险要单独评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>材料清单（常见）</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>户口簿、房产证/租赁备案、入学信息登记表、人户分离凭证（如有）、居住证及社保材料（随迁）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>权威查询</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>市教委官网、各区教育局当年实施方案、shrxbm.edu.sh.gov.cn、上海教育考试院（中考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>三、本册其他政策页</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>工作表</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>幼升小政策</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>信息登记、人户一致、公民办报名、验证与统筹</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>小升初政策</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>三种入学方式、十六区对照、回户籍、民办初中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>中考政策</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>750分构成、三大批次、名额分配到区/到校</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>主要参考：上海市教委义务教育招生实施意见及政策问答；上海市教委高中阶段学校招生工作若干意见；上海教育考试院中招规则公开信息。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>上海 · 幼升小（幼儿园→小学）政策要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>依据市教委义务教育招生实施意见及政策问答整理；2026年口径与2025年总体保持一致。具体日期、对口、年限以当年各区4月细则为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>一、政策要点总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>政策项</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>内容要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>核心原则</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>免试就近入学；严禁以考试/竞赛/培训成绩或证书作为招生依据；公民办同步招生，超额摇号</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>报名系统</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>「一网通办」义务教育入学专栏 或 上海市义务教育入学报名系统（shrxbm.edu.sh.gov.cn）；亦可经「随申办」办理</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>入学对象（以当年文件为准）</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>年满6周岁适龄儿童（如2026年对象为2019.9.1—2020.8.31出生）；特殊原因可申请推迟一年</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>信息登记</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>通常4月中下旬完成；在园儿童由幼儿园协助登记，未入园按区指定方式登记；登记后明确一名关联监护人</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>公民办二选一</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>公办报名与民办报名只能选择其一；提交后不可改报、不可放弃志愿后再报另一类</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>公办路径</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>按户籍/对口地段就近入学；人户一致优先；超额时按入户年限、房产登记时间、与户主关系等排序（各区细则不同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>民办路径</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>网上报名 → 报名人数≤计划则全部录取，超过计划则电脑随机录取；可填1个志愿+1个调剂志愿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>人户一致</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>儿童户籍地址与本人或直系亲属自有住宅类房产地址一致，通常为公办最优入学类别</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>人户分离</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>确有困难不能在户籍地入学，可凭有效《本市户籍人户分离人员居住登记凭证》申请居住地入学；人户一致优先后再统筹</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>五年一户</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>部分区/校实行「同一地址五年内仅享有一次同校对口入学机会」；热门小学常见预警，买房前必须核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>随迁子女</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>儿童持有效居住证/登记凭证；父母一方持有效居住证，且满足社保满6个月或灵活就业登记连续3年等条件（以当年文件为准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>验证与告知</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>公办通常5月中下旬分批验证；通过后发送入学告知；民办未录取者按「人户一致优先、同类排序靠后」统筹进公办</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>校园开放日</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>约4月中旬；不与招生挂钩，不得测试/收简历/变相报名</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>二、典型时间线（日期每年微调）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>约3月底</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>市教委发布当年义务教育招生实施意见与政策问答</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>4月7日前后</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>各区公布实施方案、对口划片、人户分离细则</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>4月中旬</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>校园开放日（不挂钩招生）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>4月中下旬</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>幼升小入学信息登记；人户分离居住地入学申请截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>5月上旬</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>公办/民办小学报名（公民办二选一；民办通常更短窗口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>5月中下旬</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>公办验证；民办超额摇号；陆续发放入学告知</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>5月底</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>公办第二批验证（含民办未录取统筹）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>8月中旬前</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>发放入学通知书；开学前完成学籍对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>三、入学优先级（理解「抢学位」的本质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>人户一致（户籍=自有住房地址）</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>最优，对口确定性最高</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>人户分离但符合居住地入学条件</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>次优，可能被统筹</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>集体户口 / 廉租房等特殊路径</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>按区细则就近或统筹</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>随迁子女（居住证+社保等）</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>另行排序，热门校机会通常更弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>材料不齐 / 错过节点</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>风险最大，可能无法按意愿入学</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>四、与本选房策略的衔接</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>关注点</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>操作建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>空心化板块</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>居住适龄人口少 → 对口校更不易触发「超额排序/统筹」，人户一致更「稳」</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>潍坊等老破小</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>总价友好，但须核对明珠/浦师附小等当年入户年限与五年一户</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>不要只看校名</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>先看能否在入学年满足人户一致+年限，再看小学口碑</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>上海 · 小升初政策要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>公办初中入学方式因区而异（对口 / 派位）。买房前先确认目标区属于哪一类，再决定「一步到位」还是「小学后再置换」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>一、政策要点总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>政策项</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>内容要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>核心原则</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>免试入学；公办初中采取小学划片对口、居住地段对口或电脑派位等方式；公民办同步招生</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>信息核对</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>系统对接小学五年级学籍；约4月中下旬核对户籍/居住地址等，截止日后不可随意更改</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>三种公办方式</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>①小学划片对口（学籍对口）②居住地段对口（户籍/房产对口）③电脑派位；各区采用组合不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>学籍对口区（常见）</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>黄浦、杨浦、虹口、普陀等：小学毕业后按学籍对口进入初中，小学选择影响更大</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>户籍对口区（常见）</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>浦东、闵行、宝山、嘉定、松江、青浦、奉贤、金山、崇明等：更强调户籍/居住地段对口</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>学籍+派位区（常见）</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>徐汇、长宁、静安等：学籍对口为主，部分热门学校结合电脑派位</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>回户籍/居住地</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>跨区就读小学生可申请回户籍（居住）地读初中；网上填申请表，由目标区统筹安排；有明确截止日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>民办初中</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>约5月中旬网上报名；1个志愿+1个调剂；超额电脑摇号；未录取按对口生源优先、同类靠后统筹公办</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>民办一贯制直升</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>一贯制学校通常先征求本校直升意愿并完成直升录取，再进行校外招生</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>购买学位民办校</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>部分民办校纳入区购买学位政策，仍属民办、同步招生、超额摇号；学费与生均标准差额规则见简章</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>外省市回沪读六年级</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>本市户籍或符合条件非本市户籍，在外地读五年级需回沪的，向户籍/居住地区登记后统筹安排</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>与买房关系</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>不必一步买「小初双优」；可先锁定小学，再视小升初规则置换初中学区（纪要策略）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>二、典型时间线</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>约3月底</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>市级招生意见发布；各区随后公布初中划片方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>4月中下旬</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>五年级信息核对；回户籍/居住地申请截止；一贯制征求直升意愿</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>5月上旬</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>民办一贯制直升录取（约）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>5月中旬</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>民办初中网上报名</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>5月中下旬</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>民办摇号/调剂；公办按对口或派位分配；发放入学信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>入学通知与报到</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>三、十六区公办小升初方式对照（购房决策用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>行政区</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>常见入学方式</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>本区保护体感</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>年限/对口提示</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>与纪要策略关系</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>策略标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>黄浦</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>学籍对口</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>人户一致优先；全区五年一户较常见</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>中考相对友好、人口少</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>★★★ 策略优选区</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>杨浦</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>学籍对口</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>人户一致；热门校有入户/年限要求</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>滨江与鞍山等老破小逻辑</t>
+        </is>
+      </c>
+      <c r="F31" s="41" t="inlineStr">
+        <is>
+          <t>★★★ 策略优选区</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>虹口</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>学籍对口</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>较强</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>核验对口与年限</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>北外滩等可作次优</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr">
+        <is>
+          <t>★★ 次优观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>学籍对口</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>部分学校五年一户/预警</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>曹杨等老工人新村可看</t>
+        </is>
+      </c>
+      <c r="F33" s="38" t="inlineStr">
+        <is>
+          <t>★★ 可考虑</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>学籍+派位</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>热门双学区高门槛；九年一贯常需提前年限</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>资源顶尖但竞争与总价高</t>
+        </is>
+      </c>
+      <c r="F34" s="41" t="inlineStr">
+        <is>
+          <t>★ 谨慎/条件核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>长宁</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>学籍+派位</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>较强</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>派位规则需看当年细则</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>公办较均衡</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="inlineStr">
+        <is>
+          <t>★★ 可观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>静安</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>学籍+派位特征</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>热门一贯制竞争激烈</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>总价门槛高</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr">
+        <is>
+          <t>★★ 可观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>浦东</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>较强</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>热门小学常见入户年限预警/五年一户</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>仅潍坊等少数老板块契合空心化策略</t>
+        </is>
+      </c>
+      <c r="F37" s="38" t="inlineStr">
+        <is>
+          <t>分化极大</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>闵行</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>弱（民办开放）</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>年限与竞争双高</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>新上海人集中，纪要多数排除</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>✕ 策略排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>宝山</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>核验对口</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>人口压力大</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>✕ 策略排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>嘉定</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>尚可</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>新城热门校年限趋严</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>纪要排除</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>✕ 策略排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>松江</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>弱</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>九亭等卷度极高</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>纪要点名排除九亭</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>✕ 策略排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>青浦</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>核验对口</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>导入型为主</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>✕ 主线排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>奉贤</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>核验对口</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>远郊，通勤与资源需权衡</t>
+        </is>
+      </c>
+      <c r="F43" s="38" t="inlineStr">
+        <is>
+          <t>○ 观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>金山</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>核验对口</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>竞争低但资源与通勤弱</t>
+        </is>
+      </c>
+      <c r="F44" s="38" t="inlineStr">
+        <is>
+          <t>○ 观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>崇明</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>户籍对口</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>核验对口</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>极端空心化，多数家庭不适配</t>
+        </is>
+      </c>
+      <c r="F45" s="38" t="inlineStr">
+        <is>
+          <t>○ 观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>四、决策分流（结合纪要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>情形</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>目标在学籍对口区</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>小学对口几乎绑定初中 → 更需一次选对小学；或接受对口初中普通再谋民办摇号</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>目标在户籍对口区</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>更适合「先小学、后置换初中」；搬家时间点卡在小升初信息核对前</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>准备冲民办初中</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>公民办同步；未摇中回公办时可能排序靠后，需有保底对口</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>准备读一贯制</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>核对直升规则与入户年限；时间不够则放弃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>上海 · 中考（初升高）政策要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>中考是全市学业考试+分批次录取。学区房无法「锁定」高中；真正影响的是报名区竞争生态与名额分配结构。分数线每年变化，下表讲规则不报预测分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>一、政策要点总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>政策项</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>内容要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>考试构成</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>初中学业水平考试：语文、数学、外语、道法、历史、体育与健身、综合测试（物理/化学/跨学科/实验等），总分750分</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>综合素质评价</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>纪实报告评价；名额分配批次「合格」赋50分（满分800=750+50）；自主招生等也需结合综评</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>录取三大批次</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>依次：①自主招生 ②名额分配综合评价 ③统一招生；前一批次录取后不再进入后批次同路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>自主招生</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>市实验性示范性高中约10%计划；特色高中不超过15%；含体艺骨干、国际课程班、中职校自主招生等；可兼报类别但普高签约预录通常限1所</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>名额分配到区</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>市实验性示范性高中该批次约占本校计划65%中的「到区」部分；按报名所在区投档，区与区之间分数线差异大</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>名额分配到校</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>分配到不选择生源初中；通常要求在籍在读满3年；校内竞争，弱校也可能冲市重点</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>统一招生</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>普高+中职；平行志愿（常见1—15志愿）+征求志愿；按学业考试成绩投档</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>中本贯通</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>仅限符合条件的上海户籍；平行志愿；成绩须达普高最低投档控制线</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>志愿填报时点</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>学业考试后、成绩公布前填报各批次志愿（以当年考试院安排为准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>报名资格关键</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>中考报名资格与户籍/学籍/居住证积分等挂钩；随迁子女报考高中阶段学校有专门规定，小升初阶段就应提前了解</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>与选区关系</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>中考按报名所在区竞争「名额分配到区」；区内外头部高中供给、报名人数决定难度。黄浦等区常被视为「中考相对友好」区之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>纪要提醒</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>高中统考，不必用学区房提前锁定高中；升学主矛盾在初升高，应优先布局小学+初中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>二、录取批次结构</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>顺序</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>批次</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>主要内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>第1批</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>自主招生</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>市实验性示范性/特色高中自招、体艺、国际课程班、中职校自招等</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>第2批</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>名额分配综合评价</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>到区（区间竞争）+ 到校（校内竞争，满3年学籍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>第3批</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>统一招生</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>普高与中职平行志愿 + 征求志愿</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>三、典型时间线</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>约2—3月</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>市教委发布高中阶段招生若干意见；学校公布自主招生方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>3—5月</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>中招报名、资格确认；体艺等专项资格</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>4—5月</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>体育测试、外语听说、理化实验等（具体日程以考试院为准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>6月中旬</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>学业考试笔试</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>考试后—出分前</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>填报自主招生/名额分配/统一招生等志愿</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>出分后</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>按批次投档录取；公布各控制线与名额分配分数线</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>四、对选房/选区的含义</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>不要为高中买学区房</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>高中靠中考；学区房解决的是义务教育入场券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>区的选择仍有意义</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>影响初中资源、名额分配到区的竞争池、中考「性价比」</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>到校名额</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>在薄弱初中满3年也可能冲市重点 → 与「差异化、降竞争」思路相容</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>户籍与中本贯通</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>中本贯通通常仅上海户籍；落户时间表要与升学规划对齐</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12338,7 +14616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13086,7 +15364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13363,7 +15641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
